--- a/data/fmsForecastOutput/File1/RPT_RPT4121303682161VB_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT4121303682161VB_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>525.7446861388845</v>
+        <v>67.57698478948238</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>561.526874778127</v>
+        <v>76.82778635685057</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>602.452270023812</v>
+        <v>86.14293662094818</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>637.3706521017883</v>
+        <v>95.70578914194256</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>678.7571483337658</v>
+        <v>105.8258076667196</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>45.3147253789129</v>
+        <v>5.824561975432744</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>51.17606325962314</v>
+        <v>7.001879751968285</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>57.94880655325255</v>
+        <v>8.285935033457696</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>65.39044139336183</v>
+        <v>9.818845243743972</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>75.03547156254464</v>
+        <v>11.69886667308405</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>54216767.67339625</v>
+        <v>6968792.611690121</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>62179819.38206477</v>
+        <v>8507407.381134508</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>71375912.69682689</v>
+        <v>10205838.75210906</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>81552007.84241547</v>
+        <v>12245620.72466085</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>95046278.11887141</v>
+        <v>14818774.53863547</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>534.6164055963728</v>
+        <v>68.7173178573032</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>571.0024035513379</v>
+        <v>78.12422279276308</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>612.6183975512834</v>
+        <v>87.59656228202307</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>648.1260125742092</v>
+        <v>97.32078389911364</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>690.2108884447809</v>
+        <v>107.6115734609045</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>55.18193508189709</v>
+        <v>7.092851123365377</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>62.25301197409733</v>
+        <v>8.517421549781028</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>70.41489977249954</v>
+        <v>10.06842624733258</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>79.34775647936618</v>
+        <v>11.91463652343951</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>90.89573510807104</v>
+        <v>14.17165860409003</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>54216767.67339625</v>
+        <v>6968792.611690121</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>62179819.38206477</v>
+        <v>8507407.381134508</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>71375912.69682689</v>
+        <v>10205838.75210906</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>81552007.84241547</v>
+        <v>12245620.72466085</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>95046278.11887141</v>
+        <v>14818774.53863547</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -1980,34 +1980,34 @@
         </is>
       </c>
       <c r="AS8" s="154" t="n">
-        <v>0.985</v>
+        <v>0.66</v>
       </c>
       <c r="AT8" s="154" t="n">
-        <v>0.98</v>
+        <v>0.67</v>
       </c>
       <c r="AU8" s="154" t="n">
-        <v>0.975</v>
+        <v>0.68</v>
       </c>
       <c r="AV8" s="154" t="n">
-        <v>0.97</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AW8" s="154" t="n">
-        <v>0.965</v>
+        <v>0.7</v>
       </c>
       <c r="AX8" s="154" t="n">
-        <v>0.97</v>
+        <v>0.71</v>
       </c>
       <c r="AY8" s="154" t="n">
-        <v>0.9675</v>
+        <v>0.72</v>
       </c>
       <c r="AZ8" s="154" t="n">
-        <v>0.965</v>
+        <v>0.73</v>
       </c>
       <c r="BA8" s="154" t="n">
-        <v>0.9625</v>
+        <v>0.74</v>
       </c>
       <c r="BB8" s="154" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="BD8" s="31" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>1562.899820031829</v>
+        <v>200.9392608743728</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>1676.470624165207</v>
+        <v>229.4358624462139</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>1807.173200207154</v>
+        <v>258.4780534123347</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1906.50187558952</v>
+        <v>286.372557143136</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>2020.325454925211</v>
+        <v>315.1024756450205</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>102.0875524931832</v>
+        <v>13.12521575569457</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>111.3783079576457</v>
+        <v>15.2428427767931</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>124.2656707215848</v>
+        <v>17.77358621210824</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>139.4255160231355</v>
+        <v>20.94288081526296</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>159.3176458849825</v>
+        <v>24.84816716530113</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>27075095.88191496</v>
+        <v>3480997.108633599</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>29709194.45280087</v>
+        <v>4065895.670110425</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>33317745.29128101</v>
+        <v>4765401.537600891</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>37537461.76319914</v>
+        <v>5638441.299967805</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>43164315.19002542</v>
+        <v>6732174.037970761</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1587.472936028264</v>
+        <v>204.098582861884</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1702.829387909507</v>
+        <v>233.0432299750668</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1835.586970626191</v>
+        <v>262.5420446596461</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1936.477368027242</v>
+        <v>290.8751272853033</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>2052.090569437423</v>
+        <v>320.0567597171955</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>102.5208428424309</v>
+        <v>13.18092312823753</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>111.8525414714574</v>
+        <v>15.30774470449401</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>124.7982869666684</v>
+        <v>17.84976574499927</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>140.0305064644363</v>
+        <v>21.03375544903109</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>160.020030537208</v>
+        <v>24.95771542755353</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>27075095.88191496</v>
+        <v>3480997.108633599</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>29709194.45280087</v>
+        <v>4065895.670110425</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>33317745.29128101</v>
+        <v>4765401.537600891</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>37537461.76319914</v>
+        <v>5638441.299967805</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>43164315.19002542</v>
+        <v>6732174.037970761</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2128,34 +2128,34 @@
         </is>
       </c>
       <c r="AS9" s="154" t="n">
-        <v>0.98222200886944</v>
+        <v>0.87</v>
       </c>
       <c r="AT9" s="154" t="n">
-        <v>0.959877939943838</v>
+        <v>0.89</v>
       </c>
       <c r="AU9" s="154" t="n">
-        <v>0.953844334714395</v>
+        <v>0.91</v>
       </c>
       <c r="AV9" s="154" t="n">
-        <v>0.942019789921236</v>
+        <v>0.93</v>
       </c>
       <c r="AW9" s="154" t="n">
-        <v>0.9396716375637419</v>
+        <v>0.95</v>
       </c>
       <c r="AX9" s="154" t="n">
-        <v>0.959183430955845</v>
+        <v>0.97</v>
       </c>
       <c r="AY9" s="154" t="n">
-        <v>0.958736584295856</v>
+        <v>0.99</v>
       </c>
       <c r="AZ9" s="154" t="n">
-        <v>0.957337586100609</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" s="154" t="n">
-        <v>0.95373489701852</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" s="154" t="n">
-        <v>0.951703088585464</v>
+        <v>1.05</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>674.915961658558</v>
+        <v>86.75812768670629</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>715.3415380202639</v>
+        <v>97.88118913579783</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>764.6783632314653</v>
+        <v>109.349350670131</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>806.621388744405</v>
+        <v>121.1330186830971</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>856.3504122896179</v>
+        <v>133.5292994333823</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>55.61598365125351</v>
+        <v>7.149243587571683</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>62.01347043658532</v>
+        <v>8.485390413045844</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>69.80399040697361</v>
+        <v>9.982002096842551</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>78.53514688418744</v>
+        <v>11.79388440171466</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>89.88622615389882</v>
+        <v>14.01581015760805</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>81291863.5553112</v>
+        <v>10449789.72032372</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>91889013.83486563</v>
+        <v>12573303.05124493</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>104693657.9881079</v>
+        <v>14971240.28970995</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>119089469.6056146</v>
+        <v>17884062.02462866</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>138210593.3088968</v>
+        <v>21550948.57660624</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>686.1929673934923</v>
+        <v>88.20774802324549</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>727.2988452767501</v>
+        <v>99.5173243116833</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>777.463269024956</v>
+        <v>111.17759796222</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>820.1087615790108</v>
+        <v>123.1584623526524</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>870.6702648551105</v>
+        <v>135.7621702928089</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>65.21071091640233</v>
+        <v>8.382612807560628</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>72.67201567385089</v>
+        <v>9.943814154477863</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>81.75228062072243</v>
+        <v>11.69061298387013</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>91.90094707753259</v>
+        <v>13.80107110309291</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>105.0706821249251</v>
+        <v>16.38349719201617</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>81291863.5553112</v>
+        <v>10449789.72032372</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>91889013.83486563</v>
+        <v>12573303.05124493</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>104693657.9881079</v>
+        <v>14971240.28970995</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>119089469.6056146</v>
+        <v>17884062.02462866</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>138210593.3088968</v>
+        <v>21550948.57660624</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="AS10" s="154" t="n">
-        <v>0.980726167491445</v>
+        <v>0.86</v>
       </c>
       <c r="AT10" s="154" t="n">
         <v>0.9490429845289819</v>
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>1523.353343487998</v>
+        <v>195.8351438583047</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>1638.022615832569</v>
+        <v>224.1526512082774</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1779.022631339218</v>
+        <v>254.4284207442138</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1907.795609550436</v>
+        <v>286.5416049610097</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>2065.714141544101</v>
+        <v>322.15416792773</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>163.1362207566319</v>
+        <v>20.97202556251645</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>182.2754307563951</v>
+        <v>24.94319715690239</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>206.3389190165572</v>
+        <v>29.50973437810114</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>233.6586133253074</v>
+        <v>35.09438523709293</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>268.3575864222934</v>
+        <v>41.8511512422263</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>10322723.77456103</v>
+        <v>1327040.836613773</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>11683955.7626834</v>
+        <v>1598872.711213785</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>13388452.67630732</v>
+        <v>1914760.841506121</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>15335881.89967438</v>
+        <v>2303374.738377089</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>17864346.9842009</v>
+        <v>2785997.21158206</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>2005.546509294253</v>
+        <v>257.8236302438362</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>2156.512507995119</v>
+        <v>295.1045921824605</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>2342.143825980947</v>
+        <v>334.963672919413</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>2511.677833338426</v>
+        <v>377.2417726023483</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>2719.582953937429</v>
+        <v>424.1269234770575</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>187.5477154645968</v>
+        <v>24.11025255257538</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>209.6755471537865</v>
+        <v>28.69272336888875</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>237.5151288471992</v>
+        <v>33.96842629818612</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>269.2110311756689</v>
+        <v>40.43418517168217</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>309.5170540836088</v>
+        <v>48.2700907218524</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>10322723.77456103</v>
+        <v>1327040.836613773</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>11683955.7626834</v>
+        <v>1598872.711213785</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>13388452.67630732</v>
+        <v>1914760.841506121</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>15335881.89967438</v>
+        <v>2303374.738377089</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>17864346.9842009</v>
+        <v>2785997.21158206</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2424,34 +2424,34 @@
         </is>
       </c>
       <c r="AS11" s="154" t="n">
-        <v>0.985</v>
+        <v>0.85</v>
       </c>
       <c r="AT11" s="154" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="AU11" s="154" t="n">
-        <v>0.975</v>
+        <v>0.87</v>
       </c>
       <c r="AV11" s="154" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="AW11" s="154" t="n">
-        <v>0.965</v>
+        <v>0.89</v>
       </c>
       <c r="AX11" s="154" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="AY11" s="154" t="n">
-        <v>0.968</v>
+        <v>0.91</v>
       </c>
       <c r="AZ11" s="154" t="n">
-        <v>0.965</v>
+        <v>0.92</v>
       </c>
       <c r="BA11" s="154" t="n">
-        <v>0.963</v>
+        <v>0.93</v>
       </c>
       <c r="BB11" s="154" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" thickTop="1">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>720.1062821332661</v>
+        <v>92.56789682557995</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>763.8817096615511</v>
+        <v>104.5240461204961</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>817.5294072259526</v>
+        <v>116.9085005132788</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>863.4810932088998</v>
+        <v>129.6739771926123</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>917.8561006809389</v>
+        <v>143.1223623836156</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>60.07748730676987</v>
+        <v>7.722813679778417</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>67.00024842914527</v>
+        <v>9.167829217949889</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>75.46585380382001</v>
+        <v>10.79178281561251</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>84.97080577917319</v>
+        <v>12.76056003693032</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>97.29228259059224</v>
+        <v>15.17089804788509</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>91614587.32987224</v>
+        <v>11776830.55693749</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>103572969.597549</v>
+        <v>14172175.76245872</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>118082110.6644152</v>
+        <v>16886001.13121607</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>134425351.505289</v>
+        <v>20187436.76300575</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>156074940.2930977</v>
+        <v>24336945.78818829</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>741.1282678646603</v>
+        <v>95.27022154421417</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>786.0679014429323</v>
+        <v>107.5598440767304</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>841.1790250669774</v>
+        <v>120.2904477986835</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>888.3654199818525</v>
+        <v>133.4110012546189</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>944.1392633050566</v>
+        <v>147.2207263024105</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>70.38378063768404</v>
+        <v>9.047662415834393</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>78.45494342031294</v>
+        <v>10.73520680064329</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>88.31940133143677</v>
+        <v>12.62986833822236</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>99.36735825300116</v>
+        <v>14.92257404259399</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>113.6642322783113</v>
+        <v>17.72379508086628</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>91614587.32987224</v>
+        <v>11776830.55693749</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>103572969.597549</v>
+        <v>14172175.76245872</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>118082110.6644152</v>
+        <v>16886001.13121607</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>134425351.505289</v>
+        <v>20187436.76300575</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>156074940.2930977</v>
+        <v>24336945.78818829</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="AS12" s="154" t="n">
-        <v>0.9822</v>
+        <v>0.84</v>
       </c>
       <c r="AT12" s="154" t="n">
         <v>0.9599</v>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="AS13" s="154" t="n">
-        <v>0.9657</v>
+        <v>0.83</v>
       </c>
       <c r="AT13" s="154" t="n">
         <v>0.9340000000000001</v>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>720.1062821332661</v>
+        <v>92.56789682557996</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>763.8817096615513</v>
+        <v>104.5240461204961</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>817.5294072259525</v>
+        <v>116.9085005132788</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>863.4810932088998</v>
+        <v>129.6739771926123</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>917.8561006809389</v>
+        <v>143.1223623836156</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>60.07748730676987</v>
+        <v>7.722813679778419</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>67.00024842914529</v>
+        <v>9.167829217949889</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>75.46585380382</v>
+        <v>10.79178281561251</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>84.97080577917319</v>
+        <v>12.76056003693032</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>97.29228259059224</v>
+        <v>15.17089804788509</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>91614587.32987224</v>
+        <v>11776830.55693749</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>103572969.5975491</v>
+        <v>14172175.76245872</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>118082110.6644152</v>
+        <v>16886001.13121607</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>134425351.505289</v>
+        <v>20187436.76300574</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>156074940.2930977</v>
+        <v>24336945.78818829</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>741.1282678646603</v>
+        <v>95.27022154421418</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>786.0679014429326</v>
+        <v>107.5598440767304</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>841.1790250669771</v>
+        <v>120.2904477986835</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>888.3654199818524</v>
+        <v>133.4110012546188</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>944.1392633050566</v>
+        <v>147.2207263024104</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>70.38378063768404</v>
+        <v>9.047662415834393</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>78.45494342031296</v>
+        <v>10.73520680064329</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>88.31940133143674</v>
+        <v>12.62986833822236</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>99.36735825300117</v>
+        <v>14.92257404259399</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>113.6642322783113</v>
+        <v>17.72379508086628</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>91614587.32987224</v>
+        <v>11776830.55693749</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>103572969.5975491</v>
+        <v>14172175.76245872</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>118082110.6644152</v>
+        <v>16886001.13121607</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>134425351.505289</v>
+        <v>20187436.76300574</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>156074940.2930977</v>
+        <v>24336945.78818829</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="AW16" s="176" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" thickBot="1">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="AW17" s="177" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18" ht="30.3" customHeight="1" thickBot="1">
@@ -3214,7 +3214,7 @@
         <v>125827.3950747779</v>
       </c>
       <c r="X19" s="76" t="n">
-        <v>137706.1412824631</v>
+        <v>137706.1412824632</v>
       </c>
       <c r="Y19" s="74" t="n">
         <v>881096.8938544564</v>
@@ -3295,7 +3295,7 @@
         <v>17721.27350432666</v>
       </c>
       <c r="E20" s="80" t="n">
-        <v>18436.38744059608</v>
+        <v>18436.38744059609</v>
       </c>
       <c r="F20" s="80" t="n">
         <v>19689.18165978304</v>
@@ -3345,10 +3345,10 @@
         <v>17446.95896355983</v>
       </c>
       <c r="V20" s="80" t="n">
-        <v>18151.00337082639</v>
+        <v>18151.0033708264</v>
       </c>
       <c r="W20" s="80" t="n">
-        <v>19384.40509709642</v>
+        <v>19384.40509709643</v>
       </c>
       <c r="X20" s="81" t="n">
         <v>21034.31292599275</v>
@@ -3418,7 +3418,7 @@
         <v>136912.0182055125</v>
       </c>
       <c r="F21" s="86" t="n">
-        <v>147639.8608658152</v>
+        <v>147639.8608658153</v>
       </c>
       <c r="G21" s="87" t="n">
         <v>161394.904849014</v>
@@ -3566,16 +3566,16 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>6776.316091528215</v>
+        <v>6776.316091528216</v>
       </c>
       <c r="D22" s="80" t="n">
-        <v>7132.963641496925</v>
+        <v>7132.963641496926</v>
       </c>
       <c r="E22" s="80" t="n">
-        <v>7525.734884119331</v>
+        <v>7525.734884119332</v>
       </c>
       <c r="F22" s="80" t="n">
-        <v>8038.535062615124</v>
+        <v>8038.535062615125</v>
       </c>
       <c r="G22" s="81" t="n">
         <v>8648.024731460415</v>
@@ -3619,7 +3619,7 @@
         <v>5147.087702390689</v>
       </c>
       <c r="U22" s="80" t="n">
-        <v>5417.986549749169</v>
+        <v>5417.98654974917</v>
       </c>
       <c r="V22" s="80" t="n">
         <v>5716.323877206774</v>
@@ -3655,7 +3655,7 @@
         <v>56368.84160301436</v>
       </c>
       <c r="AG22" s="80" t="n">
-        <v>56966.02339325099</v>
+        <v>56966.023393251</v>
       </c>
       <c r="AH22" s="81" t="n">
         <v>57716.84224991126</v>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="AS22" s="178" t="n">
-        <v>0.97222200886944</v>
+        <v>0.25</v>
       </c>
       <c r="AT22" s="178" t="n">
-        <v>0.949877939943838</v>
+        <v>0.26</v>
       </c>
       <c r="AU22" s="178" t="n">
-        <v>0.943844334714395</v>
+        <v>0.27</v>
       </c>
       <c r="AV22" s="178" t="n">
-        <v>0.932019789921236</v>
+        <v>0.2799999999999999</v>
       </c>
       <c r="AW22" s="178" t="n">
-        <v>0.9296716375637419</v>
+        <v>0.2899999999999999</v>
       </c>
       <c r="AX22" s="178" t="n">
-        <v>0.949183430955845</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="AY22" s="178" t="n">
-        <v>0.9487365842958559</v>
+        <v>0.3099999999999999</v>
       </c>
       <c r="AZ22" s="178" t="n">
-        <v>0.947337586100609</v>
+        <v>0.32</v>
       </c>
       <c r="BA22" s="178" t="n">
-        <v>0.94373489701852</v>
+        <v>0.33</v>
       </c>
       <c r="BB22" s="178" t="n">
-        <v>0.941703088585464</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="23" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3709,10 +3709,10 @@
         <v>135587.7072163942</v>
       </c>
       <c r="E23" s="86" t="n">
-        <v>144437.7530896318</v>
+        <v>144437.7530896319</v>
       </c>
       <c r="F23" s="86" t="n">
-        <v>155678.3959284303</v>
+        <v>155678.3959284304</v>
       </c>
       <c r="G23" s="87" t="n">
         <v>170042.9295804744</v>
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="AS23" s="178" t="n">
-        <v>0.9722</v>
+        <v>0.24</v>
       </c>
       <c r="AT23" s="178" t="n">
-        <v>0.9499</v>
+        <v>0.25</v>
       </c>
       <c r="AU23" s="178" t="n">
-        <v>0.9438</v>
+        <v>0.26</v>
       </c>
       <c r="AV23" s="178" t="n">
-        <v>0.9319999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="AW23" s="178" t="n">
-        <v>0.9297</v>
+        <v>0.28</v>
       </c>
       <c r="AX23" s="178" t="n">
-        <v>0.9492</v>
+        <v>0.29</v>
       </c>
       <c r="AY23" s="178" t="n">
-        <v>0.9487</v>
+        <v>0.3</v>
       </c>
       <c r="AZ23" s="178" t="n">
-        <v>0.9473</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="BA23" s="178" t="n">
-        <v>0.9437</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="BB23" s="178" t="n">
-        <v>0.9417</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
@@ -3948,10 +3948,10 @@
         <v>135587.7072163942</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>144437.7530896318</v>
+        <v>144437.7530896319</v>
       </c>
       <c r="F25" s="92" t="n">
-        <v>155678.3959284303</v>
+        <v>155678.3959284304</v>
       </c>
       <c r="G25" s="93" t="n">
         <v>170042.9295804744</v>
@@ -4411,7 +4411,7 @@
         <v>540.56924056598</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>590.9387062588255</v>
+        <v>590.9387062588254</v>
       </c>
       <c r="E35" s="149" t="n">
         <v>638.0531763714454</v>
@@ -4420,10 +4420,10 @@
         <v>683.5994754926789</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>729.8190325574334</v>
+        <v>729.8190325574333</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>46.59247602564243</v>
+        <v>46.59247602564245</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>53.85657921717609</v>
@@ -4432,13 +4432,13 @@
         <v>61.37319407357498</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>70.13324396304046</v>
+        <v>70.13324396304044</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>80.68027776606016</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>55745531.43349849</v>
+        <v>55745531.4334985</v>
       </c>
       <c r="N35" s="152" t="n">
         <v>65436693.54305337</v>
@@ -4458,22 +4458,22 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>549.6911181162211</v>
+        <v>549.6911181162212</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>600.9105472621114</v>
+        <v>600.9105472621113</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>648.8200541525581</v>
+        <v>648.820054152558</v>
       </c>
       <c r="W35" s="149" t="n">
         <v>695.134927828673</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>742.1344203916619</v>
+        <v>742.1344203916617</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>56.73791390884794</v>
+        <v>56.73791390884796</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>65.51371983972091</v>
@@ -4488,7 +4488,7 @@
         <v>97.73368519656307</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>55745531.43349849</v>
+        <v>55745531.4334985</v>
       </c>
       <c r="AE35" s="152" t="n">
         <v>65436693.54305337</v>
@@ -4516,7 +4516,7 @@
         <v>1764.891249586261</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1914.652247498776</v>
+        <v>1914.652247498775</v>
       </c>
       <c r="F36" s="156" t="n">
         <v>2045.518265308115</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1632.788662895073</v>
+        <v>1632.788662895072</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>1792.640230577437</v>
@@ -4612,22 +4612,22 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>694.0250915277945</v>
+        <v>694.0250915277946</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>752.8940651847132</v>
+        <v>752.8940651847131</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>809.958282950766</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>865.2243178712511</v>
+        <v>865.2243178712509</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>920.8794661320744</v>
+        <v>920.8794661320742</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>57.19065829931702</v>
+        <v>57.19065829931704</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>65.26892592093562</v>
@@ -4636,13 +4636,13 @@
         <v>73.93738718357088</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>84.24090885757698</v>
+        <v>84.24090885757697</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>96.65947346474205</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>83593508.30256727</v>
+        <v>83593508.30256729</v>
       </c>
       <c r="N37" s="165" t="n">
         <v>96712814.08236434</v>
@@ -4662,25 +4662,25 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>705.6213870400744</v>
+        <v>705.6213870400745</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>765.4790825372824</v>
+        <v>765.4790825372822</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>823.5002384213285</v>
+        <v>823.5002384213284</v>
       </c>
       <c r="W37" s="162" t="n">
         <v>879.6915798649629</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>936.2783705949603</v>
+        <v>936.2783705949599</v>
       </c>
       <c r="Y37" s="161" t="n">
         <v>67.05704440761882</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>76.48700151996887</v>
+        <v>76.48700151996886</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>86.59318744033327</v>
@@ -4692,7 +4692,7 @@
         <v>112.9881322794418</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>83593508.30256727</v>
+        <v>83593508.30256729</v>
       </c>
       <c r="AE37" s="165" t="n">
         <v>96712814.08236434</v>
@@ -4741,7 +4741,7 @@
         <v>250.6700069020689</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>288.6233076017104</v>
+        <v>288.6233076017105</v>
       </c>
       <c r="M38" s="158" t="n">
         <v>10616235.42155413</v>
@@ -4776,10 +4776,10 @@
         <v>2694.539229085312</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>2924.959334771552</v>
+        <v>2924.959334771553</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>192.8803621630839</v>
+        <v>192.880362163084</v>
       </c>
       <c r="Z38" s="156" t="n">
         <v>220.7106826995256</v>
@@ -4791,7 +4791,7 @@
         <v>288.8108000066136</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>332.8910395257876</v>
+        <v>332.8910395257877</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>10616235.42155413</v>
@@ -4819,19 +4819,19 @@
         <v>740.5046540201391</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>803.9939146639028</v>
+        <v>803.9939146639026</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>865.9524924915712</v>
+        <v>865.952492491571</v>
       </c>
       <c r="F39" s="162" t="n">
         <v>926.2300002366521</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>987.0370608328327</v>
+        <v>987.0370608328326</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>61.77929571827543</v>
+        <v>61.77929571827545</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>70.51849957484833</v>
@@ -4840,13 +4840,13 @@
         <v>79.93577187781914</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>91.14560825469262</v>
+        <v>91.14560825469263</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>104.6254293877788</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>94209743.72412141</v>
+        <v>94209743.72412142</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>109011691.5052119</v>
@@ -4866,22 +4866,22 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>762.1221272419066</v>
+        <v>762.1221272419065</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>827.3451259263115</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>891.0029008743099</v>
+        <v>891.0029008743098</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>952.9226634276281</v>
+        <v>952.9226634276282</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>1015.301246870986</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>72.37753429304497</v>
+        <v>72.37753429304499</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>82.57469224283393</v>
@@ -4896,7 +4896,7 @@
         <v>122.2313711992247</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>94209743.72412141</v>
+        <v>94209743.72412142</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>109011691.5052119</v>
@@ -5023,19 +5023,19 @@
         <v>740.5046540201391</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>803.9939146639028</v>
+        <v>803.9939146639026</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>865.9524924915712</v>
+        <v>865.952492491571</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>926.2300002366521</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>987.0370608328327</v>
+        <v>987.0370608328326</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>61.77929571827543</v>
+        <v>61.77929571827545</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>70.51849957484833</v>
@@ -5044,13 +5044,13 @@
         <v>79.93577187781914</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>91.14560825469262</v>
+        <v>91.14560825469263</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>104.6254293877788</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>94209743.72412141</v>
+        <v>94209743.72412142</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>109011691.5052119</v>
@@ -5070,22 +5070,22 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>762.1221272419066</v>
+        <v>762.1221272419065</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>827.3451259263115</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>891.0029008743099</v>
+        <v>891.0029008743098</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>952.9226634276281</v>
+        <v>952.9226634276282</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1015.301246870986</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>72.37753429304497</v>
+        <v>72.37753429304499</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>82.57469224283393</v>
@@ -5100,7 +5100,7 @@
         <v>122.2313711992247</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>94209743.72412141</v>
+        <v>94209743.72412142</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>109011691.5052119</v>
@@ -5374,7 +5374,7 @@
         <v>0.181917220935476</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.2017575055825044</v>
+        <v>0.2017575055825043</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.2252303983415999</v>
@@ -5383,7 +5383,7 @@
         <v>0.2493034041864279</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2729444976956166</v>
+        <v>0.2729444976956165</v>
       </c>
       <c r="H46" s="148" t="n">
         <v>0.01567971893149758</v>
@@ -5430,7 +5430,7 @@
         <v>0.229031066156352</v>
       </c>
       <c r="W46" s="149" t="n">
-        <v>0.2535102938042424</v>
+        <v>0.2535102938042423</v>
       </c>
       <c r="X46" s="150" t="n">
         <v>0.2775503207783075</v>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="C47" s="155" t="n">
-        <v>0.04036638471954133</v>
+        <v>0.04036638471954132</v>
       </c>
       <c r="D47" s="156" t="n">
         <v>0.04143667480756179</v>
@@ -5482,7 +5482,7 @@
         <v>0.041874974291546</v>
       </c>
       <c r="F47" s="156" t="n">
-        <v>0.04117045304614886</v>
+        <v>0.04117045304614885</v>
       </c>
       <c r="G47" s="157" t="n">
         <v>0.03973543022225098</v>
@@ -5523,16 +5523,16 @@
         </is>
       </c>
       <c r="T47" s="155" t="n">
-        <v>0.04100105614336285</v>
+        <v>0.04100105614336284</v>
       </c>
       <c r="U47" s="156" t="n">
         <v>0.04208817415736146</v>
       </c>
       <c r="V47" s="156" t="n">
-        <v>0.04253336492377023</v>
+        <v>0.04253336492377022</v>
       </c>
       <c r="W47" s="156" t="n">
-        <v>0.04181776665215349</v>
+        <v>0.04181776665215348</v>
       </c>
       <c r="X47" s="157" t="n">
         <v>0.04036018129298802</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>0.1615583391258172</v>
+        <v>0.1615583391258171</v>
       </c>
       <c r="D48" s="162" t="n">
         <v>0.1796400717568933</v>
@@ -5587,7 +5587,7 @@
         <v>0.221546892764948</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.2420728981853963</v>
+        <v>0.2420728981853962</v>
       </c>
       <c r="H48" s="161" t="n">
         <v>0.01331310334617744</v>
@@ -5637,13 +5637,13 @@
         <v>0.2252513389707702</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.246120830156198</v>
+        <v>0.2461208301561979</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.01560984588803904</v>
       </c>
       <c r="Z48" s="162" t="n">
-        <v>0.01824975262375836</v>
+        <v>0.01824975262375835</v>
       </c>
       <c r="AA48" s="162" t="n">
         <v>0.0214398674269464</v>
@@ -5689,10 +5689,10 @@
         <v>0.2265826015246186</v>
       </c>
       <c r="G49" s="157" t="n">
-        <v>0.235224249840784</v>
+        <v>0.2352242498407841</v>
       </c>
       <c r="H49" s="155" t="n">
-        <v>0.02135684474724433</v>
+        <v>0.02135684474724434</v>
       </c>
       <c r="I49" s="156" t="n">
         <v>0.02314558103992517</v>
@@ -5701,22 +5701,22 @@
         <v>0.0252706175829999</v>
       </c>
       <c r="K49" s="156" t="n">
-        <v>0.02775086398713267</v>
+        <v>0.02775086398713268</v>
       </c>
       <c r="L49" s="157" t="n">
-        <v>0.03055805771271074</v>
+        <v>0.03055805771271075</v>
       </c>
       <c r="M49" s="158" t="n">
-        <v>1351.390929613805</v>
+        <v>1351.390929613806</v>
       </c>
       <c r="N49" s="159" t="n">
         <v>1483.644525484691</v>
       </c>
       <c r="O49" s="159" t="n">
-        <v>1639.702627229063</v>
+        <v>1639.702627229064</v>
       </c>
       <c r="P49" s="159" t="n">
-        <v>1821.392186934197</v>
+        <v>1821.392186934198</v>
       </c>
       <c r="Q49" s="160" t="n">
         <v>2034.225130062324</v>
@@ -5742,7 +5742,7 @@
         <v>0.3096807284968951</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.024552655586236</v>
+        <v>0.02455265558623601</v>
       </c>
       <c r="Z49" s="156" t="n">
         <v>0.02662488492606867</v>
@@ -5757,16 +5757,16 @@
         <v>0.03524491380270291</v>
       </c>
       <c r="AD49" s="158" t="n">
-        <v>1351.390929613805</v>
+        <v>1351.390929613806</v>
       </c>
       <c r="AE49" s="159" t="n">
         <v>1483.644525484691</v>
       </c>
       <c r="AF49" s="159" t="n">
-        <v>1639.702627229063</v>
+        <v>1639.702627229064</v>
       </c>
       <c r="AG49" s="159" t="n">
-        <v>1821.392186934197</v>
+        <v>1821.392186934198</v>
       </c>
       <c r="AH49" s="160" t="n">
         <v>2034.225130062324</v>
@@ -5788,10 +5788,10 @@
         <v>0.2014434506623188</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.2218069142097241</v>
+        <v>0.221806914209724</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.2417245903762601</v>
+        <v>0.24172459037626</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.01364687476103878</v>
@@ -5835,7 +5835,7 @@
         <v>0.1863927344479899</v>
       </c>
       <c r="V50" s="162" t="n">
-        <v>0.2072708381331948</v>
+        <v>0.2072708381331947</v>
       </c>
       <c r="W50" s="162" t="n">
         <v>0.2281990816550855</v>
@@ -5992,10 +5992,10 @@
         <v>0.2014434506623188</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.2218069142097241</v>
+        <v>0.221806914209724</v>
       </c>
       <c r="G52" s="181" t="n">
-        <v>0.2417245903762601</v>
+        <v>0.24172459037626</v>
       </c>
       <c r="H52" s="179" t="n">
         <v>0.01364687476103878</v>
@@ -6039,7 +6039,7 @@
         <v>0.1863927344479899</v>
       </c>
       <c r="V52" s="186" t="n">
-        <v>0.2072708381331948</v>
+        <v>0.2072708381331947</v>
       </c>
       <c r="W52" s="186" t="n">
         <v>0.2281990816550855</v>
@@ -6337,13 +6337,13 @@
         <v>0.01034250027988828</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.009529046918664087</v>
+        <v>0.009529046918664085</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0.00881407034960229</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0003206394028269365</v>
+        <v>0.0003206394028269364</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>0.009689845559503415</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008962804062908109</v>
+        <v>0.008962804062908107</v>
       </c>
       <c r="W57" s="149" t="n">
         <v>0.0003260500572831676</v>
@@ -6547,7 +6547,7 @@
         <v>0.007627179541740433</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002778790844920277</v>
+        <v>0.0002778790844920276</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.009002921320424568</v>
+        <v>0.009002921320424566</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008351753781564407</v>
+        <v>0.008351753781564405</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007754700832520927</v>
+        <v>0.007754700832520925</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002825254512606015</v>
@@ -6606,7 +6606,7 @@
         <v>0.000855571140373785</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.0008345108556951456</v>
+        <v>0.0008345108556951454</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0.0008154269196345155</v>
@@ -6745,10 +6745,10 @@
         <v>0.008383323812720622</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.007782301607069054</v>
+        <v>0.007782301607069052</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.007229775608787413</v>
+        <v>0.007229775608787411</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002635306532242526</v>
@@ -6792,13 +6792,13 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008628057288799442</v>
+        <v>0.008628057288799441</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.008008330891146932</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007438919682031652</v>
+        <v>0.00743891968203165</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0002711252409240848</v>
@@ -6949,10 +6949,10 @@
         <v>0.008383323812720622</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.007782301607069054</v>
+        <v>0.007782301607069052</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.007229775608787413</v>
+        <v>0.007229775608787411</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.0002635306532242526</v>
@@ -6996,13 +6996,13 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.008628057288799442</v>
+        <v>0.008628057288799441</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0.008008330891146932</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.007438919682031652</v>
+        <v>0.00743891968203165</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.0002711252409240848</v>
@@ -7300,7 +7300,7 @@
         <v>0.004389790632988983</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.006387224154446727</v>
+        <v>0.006387224154446726</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.008442347676483794</v>
@@ -7309,7 +7309,7 @@
         <v>0.01031668646141137</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.01204674054031117</v>
+        <v>0.01204674054031116</v>
       </c>
       <c r="H68" s="148" t="n">
         <v>0.0003783626582433423</v>
@@ -7350,7 +7350,7 @@
         <v>0.004463866495284433</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006495005863524002</v>
+        <v>0.006495005863524001</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.008584808726729306</v>
@@ -7504,13 +7504,13 @@
         <v>0.003758418674650035</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.005506059761257968</v>
+        <v>0.005506059761257967</v>
       </c>
       <c r="E70" s="162" t="n">
         <v>0.007305512541687684</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.008940858059281079</v>
+        <v>0.008940858059281078</v>
       </c>
       <c r="G70" s="163" t="n">
         <v>0.01045202489141601</v>
@@ -7522,10 +7522,10 @@
         <v>0.0004773242655135323</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006668868270614731</v>
+        <v>0.0006668868270614732</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008705095237423818</v>
+        <v>0.0008705095237423817</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.001097089532127489</v>
@@ -7554,7 +7554,7 @@
         <v>0.003821217173064797</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005598096424639972</v>
+        <v>0.005598096424639971</v>
       </c>
       <c r="V70" s="162" t="n">
         <v>0.007427655777471079</v>
@@ -7569,10 +7569,10 @@
         <v>0.0003631402539260181</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005593642197525566</v>
+        <v>0.0005593642197525564</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007810372832603288</v>
+        <v>0.0007810372832603289</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.001018660470450389</v>
@@ -7615,7 +7615,7 @@
         <v>0.02891214347838031</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.0349399391400631</v>
+        <v>0.03493993914006311</v>
       </c>
       <c r="H71" s="155" t="n">
         <v>0.001202013507296027</v>
@@ -7624,16 +7624,16 @@
         <v>0.001876713097151192</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.002659554063444628</v>
+        <v>0.002659554063444629</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003541035171483904</v>
+        <v>0.003541035171483905</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004539058695875701</v>
+        <v>0.004539058695875702</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>76.05946338317243</v>
+        <v>76.05946338317244</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>120.2983458350366</v>
@@ -7645,7 +7645,7 @@
         <v>232.4112790863193</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>302.1614577989874</v>
+        <v>302.1614577989875</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7662,13 +7662,13 @@
         <v>0.03018847902881347</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.03806382063436034</v>
+        <v>0.03806382063436033</v>
       </c>
       <c r="X71" s="157" t="n">
         <v>0.04599961872067099</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001381881265885539</v>
+        <v>0.00138188126588554</v>
       </c>
       <c r="Z71" s="156" t="n">
         <v>0.002158825486588776</v>
@@ -7680,10 +7680,10 @@
         <v>0.004079822765263514</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.005235238901162373</v>
+        <v>0.005235238901162374</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>76.05946338317243</v>
+        <v>76.05946338317244</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>120.2983458350366</v>
@@ -7695,7 +7695,7 @@
         <v>232.4112790863193</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>302.1614577989874</v>
+        <v>302.1614577989875</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7708,13 +7708,13 @@
         <v>0.004156074374709216</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.006103634743632753</v>
+        <v>0.006103634743632752</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>0.008119619452050949</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.009972085784422388</v>
+        <v>0.009972085784422387</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.01169742855839976</v>
@@ -7726,13 +7726,13 @@
         <v>0.0005353512709779973</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007495192333084774</v>
+        <v>0.0007495192333084775</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.0009813025103450816</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.001239921512797902</v>
+        <v>0.001239921512797903</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>528.7511693736024</v>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004277402209740632</v>
+        <v>0.00427740220974063</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.006280908802263816</v>
@@ -7776,7 +7776,7 @@
         <v>0.0006268775811926822</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008771793683576049</v>
+        <v>0.000877179368357605</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.001147564003964397</v>
@@ -7912,13 +7912,13 @@
         <v>0.004156074374709216</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.006103634743632753</v>
+        <v>0.006103634743632752</v>
       </c>
       <c r="E74" s="180" t="n">
         <v>0.008119619452050949</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.009972085784422388</v>
+        <v>0.009972085784422387</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>0.01169742855839976</v>
@@ -7930,13 +7930,13 @@
         <v>0.0005353512709779973</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007495192333084774</v>
+        <v>0.0007495192333084775</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>0.0009813025103450816</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.001239921512797902</v>
+        <v>0.001239921512797903</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>528.7511693736024</v>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.004277402209740632</v>
+        <v>0.00427740220974063</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.006280908802263816</v>
@@ -7980,7 +7980,7 @@
         <v>0.0006268775811926822</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008771793683576049</v>
+        <v>0.000877179368357605</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.001147564003964397</v>
@@ -8263,7 +8263,7 @@
         <v>540.7658900778283</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>591.1563800354811</v>
+        <v>591.156380035481</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>638.295663187813</v>
@@ -8272,10 +8272,10 @@
         <v>683.8594162227297</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>730.1040237956693</v>
+        <v>730.1040237956691</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>46.60942554288957</v>
+        <v>46.60942554288959</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>53.87641742521999</v>
@@ -8290,7 +8290,7 @@
         <v>80.71178307249373</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>55765810.67012809</v>
+        <v>55765810.67012811</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>65460797.31568582</v>
@@ -8313,7 +8313,7 @@
         <v>549.8910860054998</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>601.1318941917834</v>
+        <v>601.1318941917833</v>
       </c>
       <c r="V79" s="149" t="n">
         <v>649.066632831504</v>
@@ -8322,10 +8322,10 @@
         <v>695.3992549487214</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>742.4242207366376</v>
+        <v>742.4242207366374</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>56.75855415663893</v>
+        <v>56.75855415663894</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>65.5378519851858</v>
@@ -8340,7 +8340,7 @@
         <v>97.77184978630244</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>55765810.67012809</v>
+        <v>55765810.67012811</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>65460797.31568582</v>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>1607.554453379703</v>
+        <v>1607.554453379702</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>1764.932686261068</v>
@@ -8467,19 +8467,19 @@
         <v>694.1992632514566</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>753.0874257612757</v>
+        <v>753.0874257612755</v>
       </c>
       <c r="E81" s="162" t="n">
         <v>810.1737556474518</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>865.4550835011598</v>
+        <v>865.4550835011597</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>921.1319910551513</v>
+        <v>921.131991055151</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>57.20501079990375</v>
+        <v>57.20501079990376</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>65.28568848785078</v>
@@ -8488,13 +8488,13 @@
         <v>73.95705670055428</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>84.26337691123091</v>
+        <v>84.26337691123089</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>96.68597956787393</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>83614486.83145009</v>
+        <v>83614486.8314501</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>96737652.16564415</v>
@@ -8517,22 +8517,22 @@
         <v>705.7984689564689</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>765.6756752368271</v>
+        <v>765.675675236827</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>823.7193136759794</v>
+        <v>823.7193136759792</v>
       </c>
       <c r="W81" s="162" t="n">
         <v>879.9262040859423</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>936.5351182282918</v>
+        <v>936.5351182282915</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>67.07387296490116</v>
+        <v>67.07387296490117</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>76.50664514766808</v>
+        <v>76.50664514766807</v>
       </c>
       <c r="AA81" s="162" t="n">
         <v>86.61622377196309</v>
@@ -8544,7 +8544,7 @@
         <v>113.0191160514357</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>83614486.83145009</v>
+        <v>83614486.8314501</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>96737652.16564415</v>
@@ -8581,7 +8581,7 @@
         <v>2221.98208238261</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>167.7973209421773</v>
+        <v>167.7973209421774</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>191.8935320354627</v>
@@ -8593,7 +8593,7 @@
         <v>250.7012988012275</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>288.658404718119</v>
+        <v>288.6584047181191</v>
       </c>
       <c r="M82" s="158" t="n">
         <v>10617662.87194712</v>
@@ -8602,7 +8602,7 @@
         <v>12300481.36571886</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>14185021.38653858</v>
+        <v>14185021.38653859</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>16454456.59286631</v>
@@ -8622,7 +8622,7 @@
         <v>2270.304891452402</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>2481.493647184658</v>
+        <v>2481.493647184659</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>2694.8755966104</v>
@@ -8631,7 +8631,7 @@
         <v>2925.31501511877</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>192.906296699936</v>
+        <v>192.9062966999361</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>220.7394664099383</v>
@@ -8643,7 +8643,7 @@
         <v>288.8468531369479</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>332.9315196784915</v>
+        <v>332.9315196784916</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>10617662.87194712</v>
@@ -8652,7 +8652,7 @@
         <v>12300481.36571886</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>14185021.38653858</v>
+        <v>14185021.38653859</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>16454456.59286631</v>
@@ -8671,19 +8671,19 @@
         <v>740.6807688387953</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>804.1889325360537</v>
+        <v>804.1889325360535</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>866.1692853372942</v>
+        <v>866.169285337294</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>926.4620427672997</v>
+        <v>926.4620427672996</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>987.2904828517674</v>
+        <v>987.2904828517673</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>61.79398873796553</v>
+        <v>61.79398873796555</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>70.53560463930658</v>
@@ -8692,13 +8692,13 @@
         <v>79.9557839496253</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>91.1684423861626</v>
+        <v>91.16844238616258</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>104.6522919936519</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>94232149.70339721</v>
+        <v>94232149.70339723</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>109038133.531363</v>
@@ -8724,7 +8724,7 @@
         <v>827.545807900453</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>891.2259651371916</v>
+        <v>891.2259651371913</v>
       </c>
       <c r="W83" s="162" t="n">
         <v>953.1613931019818</v>
@@ -8748,7 +8748,7 @@
         <v>122.2627541351808</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>94232149.70339721</v>
+        <v>94232149.70339723</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>109038133.531363</v>
@@ -8875,19 +8875,19 @@
         <v>740.6807688387953</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>804.1889325360537</v>
+        <v>804.1889325360535</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>866.1692853372942</v>
+        <v>866.169285337294</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>926.4620427672997</v>
+        <v>926.4620427672996</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>987.2904828517674</v>
+        <v>987.2904828517673</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>61.79398873796553</v>
+        <v>61.79398873796555</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>70.53560463930658</v>
@@ -8896,13 +8896,13 @@
         <v>79.9557839496253</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>91.1684423861626</v>
+        <v>91.16844238616258</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>104.6522919936519</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>94232149.70339721</v>
+        <v>94232149.70339723</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>109038133.531363</v>
@@ -8928,7 +8928,7 @@
         <v>827.545807900453</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>891.2259651371916</v>
+        <v>891.2259651371913</v>
       </c>
       <c r="W85" s="186" t="n">
         <v>953.1613931019818</v>
@@ -8952,7 +8952,7 @@
         <v>122.2627541351808</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>94232149.70339721</v>
+        <v>94232149.70339723</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>109038133.531363</v>
@@ -9343,7 +9343,7 @@
         <v>125827.3950747779</v>
       </c>
       <c r="X90" s="76" t="n">
-        <v>137706.1412824631</v>
+        <v>137706.1412824632</v>
       </c>
       <c r="Y90" s="74" t="n">
         <v>881096.8938544564</v>
@@ -9410,7 +9410,7 @@
         <v>17721.27350432666</v>
       </c>
       <c r="E91" s="80" t="n">
-        <v>18436.38744059608</v>
+        <v>18436.38744059609</v>
       </c>
       <c r="F91" s="80" t="n">
         <v>19689.18165978304</v>
@@ -9460,10 +9460,10 @@
         <v>17446.95896355983</v>
       </c>
       <c r="V91" s="80" t="n">
-        <v>18151.00337082639</v>
+        <v>18151.0033708264</v>
       </c>
       <c r="W91" s="80" t="n">
-        <v>19384.40509709642</v>
+        <v>19384.40509709643</v>
       </c>
       <c r="X91" s="81" t="n">
         <v>21034.31292599275</v>
@@ -9533,7 +9533,7 @@
         <v>136912.0182055125</v>
       </c>
       <c r="F92" s="86" t="n">
-        <v>147639.8608658152</v>
+        <v>147639.8608658153</v>
       </c>
       <c r="G92" s="87" t="n">
         <v>161394.904849014</v>
@@ -9636,16 +9636,16 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>6776.316091528215</v>
+        <v>6776.316091528216</v>
       </c>
       <c r="D93" s="80" t="n">
-        <v>7132.963641496925</v>
+        <v>7132.963641496926</v>
       </c>
       <c r="E93" s="80" t="n">
-        <v>7525.734884119331</v>
+        <v>7525.734884119332</v>
       </c>
       <c r="F93" s="80" t="n">
-        <v>8038.535062615124</v>
+        <v>8038.535062615125</v>
       </c>
       <c r="G93" s="81" t="n">
         <v>8648.024731460415</v>
@@ -9689,7 +9689,7 @@
         <v>5147.087702390689</v>
       </c>
       <c r="U93" s="80" t="n">
-        <v>5417.986549749169</v>
+        <v>5417.98654974917</v>
       </c>
       <c r="V93" s="80" t="n">
         <v>5716.323877206774</v>
@@ -9725,7 +9725,7 @@
         <v>56368.84160301436</v>
       </c>
       <c r="AG93" s="80" t="n">
-        <v>56966.02339325099</v>
+        <v>56966.023393251</v>
       </c>
       <c r="AH93" s="81" t="n">
         <v>57716.84224991126</v>
@@ -9762,10 +9762,10 @@
         <v>135587.7072163942</v>
       </c>
       <c r="E94" s="86" t="n">
-        <v>144437.7530896318</v>
+        <v>144437.7530896319</v>
       </c>
       <c r="F94" s="86" t="n">
-        <v>155678.3959284303</v>
+        <v>155678.3959284304</v>
       </c>
       <c r="G94" s="87" t="n">
         <v>170042.9295804744</v>
@@ -9994,10 +9994,10 @@
         <v>135587.7072163942</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>144437.7530896318</v>
+        <v>144437.7530896319</v>
       </c>
       <c r="F96" s="133" t="n">
-        <v>155678.3959284303</v>
+        <v>155678.3959284304</v>
       </c>
       <c r="G96" s="134" t="n">
         <v>170042.9295804744</v>
